--- a/public/crawlability-mhaim1-september-2026.xlsx
+++ b/public/crawlability-mhaim1-september-2026.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר 9 כתובות שמפנות (301/302) ולהשאיר את כתובות היעד בלבד (במדגם של 297 כתובות שנבדקו; ייתכנו כתובות נוספות).</t>
+          <t>להסיר ממפת האתר 9 כתובות שמפנות (301/302) ולהשאיר את כתובות היעד בלבד (במדגם של 250 מתוך 341 הכתובות שאינן בסריקה; ייתכנו כתובות נוספות).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 3 כתובות (הבולטת: https://www.mhaim1.com/p/גאטו+כבד+3+ק, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): 3 כתובות (הבולטת: https://www.mhaim1.com/p/גאטו+כבד+3+ק, ללא קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>שרשרת של 2 הפניות. להגדיר הפניה ישירה ליעד הסופי ולעדכן את הקישורים הפנימיים אליו.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. אם ההפניה מכוונת וקבועה, להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד; אם הכתובת המקורית אמורה לחזור, לבטל את ההפניה.</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. אם ההפניה מכוונת וקבועה, להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד; אם הכתובת המקורית אמורה לחזור, לבטל את ההפניה.</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. אם ההפניה מכוונת וקבועה, להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד; אם הכתובת המקורית אמורה לחזור, לבטל את ההפניה.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. אם ההפניה מכוונת וקבועה, להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד; אם הכתובת המקורית אמורה לחזור, לבטל את ההפניה.</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301), לפי הסריקה מ-23.09.2026. לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301), לפי הסריקה מ-23.09.2026. לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301), לפי הסריקה מ-23.09.2026. לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301), לפי הסריקה מ-23.09.2026. לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">

--- a/public/crawlability-mhaim1-september-2026.xlsx
+++ b/public/crawlability-mhaim1-september-2026.xlsx
@@ -8,13 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום פעולות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="404 ושגיאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לולאות, שרשראות, 302" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קישורים להפניות 301" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לבדיקה" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ללא טיפול" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לולאות, שרשראות, 302" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קישורים להפניות 301" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לבדיקה" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ללא טיפול" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -527,7 +526,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת (הבולטת: https://www.mhaim1.com/אקך:03-9612081, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת; הבולטת https://www.mhaim1.com/אקך:03-9612081 (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -557,7 +556,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: כתובת אחת (הבולטת: https://mhaim1.com/c/פרימו_-_PREMOI?page=2, 10 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>שרשראות הפניות: כתובת אחת; הבולטת https://mhaim1.com/c/פרימו_-_PREMOI?page=2 (10 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -572,7 +571,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>הפניות זמניות (302/307): 4 כתובות (הבולטת: https://www.mhaim1.com/c/חול_קריסטל_לחתולים, 17734 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>הפניות זמניות (302/307): 4 כתובות; הבולטת https://www.mhaim1.com/c/חול_קריסטל_לחתולים (17734 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -587,7 +586,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 8 כתובות (הבולטת: https://www.mhaim1.com/c/חתולים, 8862 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 8 כתובות; הבולטת https://www.mhaim1.com/c/חתולים (8862 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -602,7 +601,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 1426 כתובות (הבולטת: https://mhaim1.com/page/תנאי_שימוש, 8862 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 1426 כתובות; הבולטת https://mhaim1.com/page/תנאי_שימוש (8862 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -617,7 +616,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 3 כתובות (הבולטת: https://www.mhaim1.com/p/גאטו+כבד+3+ק, ללא קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של mhaim1 ב-SE Ranking; הסריקה האחרונה: 2026-04-03.</t>
         </is>
       </c>
     </row>
@@ -625,14 +624,14 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>לבדיקה</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של mhaim1 ב-SE Ranking (הסריקה האחרונה: 2026-04-03); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להחליט אם להסיר את חסימת סורקי ה-AI (Amazonbot) בקובץ robots.txt.</t>
         </is>
       </c>
     </row>
@@ -646,21 +645,6 @@
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>להחליט אם להסיר את חסימת סורקי ה-AI (Amazonbot) בקובץ robots.txt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>לאשר שהעמוד המוגדר noindex אכן אמור להישאר מחוץ לאינדקס.</t>
         </is>
@@ -672,207 +656,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>כתובת</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בסריקה 23.09</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בבדיקה חיה 27.09</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>יעד סופי / יעד להפניה</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>קפיצות</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>קישורים נכנסים</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>עמודי מקור (עד 10)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>סוג</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>פעולה נדרשת</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>יעד מומלץ להפניית 301</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>עדיפות</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>https://www.mhaim1.com/p/גאטו+כבד+3+ק</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>https://www.mhaim1.com/p/גאטו+עוף+3+ק</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>https://www.mhaim1.com/p/חטיף+לכלבים+ג'רקי+טיים+רצועות+כבש+80+גרם+-+JERKY+TIME+SOFT+LAMB+FILLET+80G</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1205,7 +988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -69483,7 +69266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -69606,13 +69389,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -69688,25 +69471,1364 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
+          <t>https://www.mhaim1.com/p/אבקרלין_צהוב_10_ליטר_8_3_קג_litterfree_paws</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/היגיינת_הפה_-_ויטמינים_לכלבים</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/גדר_אילוף___מלונות___כלוב_הטסה___מנשאים_לכלבים</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/חטיפים_דנטליים_לכלבים</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/חטיפים_דנטליים_לכלבים</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/חטיפים_דנטליים_לכלבים</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/חטיפים_דנטלים_לכלבים</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/חטיפים_דנטליים_לכלבים</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/חטיפים_דנטליים_לכלבים</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/מיטה_לכלב_קטן</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/מיטות_לכלבים</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/מיטות_לכלבים</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/מוצרי טיפוח לכלבים</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/מזון_יבש__לחתולים_HJ6Unge_dermatosis</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/מה_מותר_לחתולים_לאכול</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/מזון_לחתולי_רחוב_20_קג</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/גלגל_ריצה_לחתולים_2NRG_GJWE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/הגיינת_הפה___ויטמינים_חתולים</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/צעצועים___משחקים_לחתולים</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/חנות_חיות_בבאר_שבע_HRJT</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/חנות_חיות_ברחובות</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/מסרק_לחתול</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/מוצרי_טיפוח___מסרקים_לכלבים</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/פרימו_-_PREMOI?page=2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/ביופט_-_BIOPET</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/אוכל_היפואלרגני_לחתולים</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/מזון_היפואלרגני_לחתולים</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/מזרנים_לכלבים</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/מיטות_ומזרונים_לכלבים</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/c/כלבים</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/p/אמיננת_גורים_גזעים_קטנים_ובינונים_15_קג</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/page/פודל_טוי</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>לא נבדק</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/12918</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/p/גאטו+כבד+3+ק</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>כתובות 404 ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>לא אותר קישור פנימי לכתובת; לאתר את המקור (canonical, hreflang, קובץ סטטי או קישור חיצוני) ולתקן. אין צורך בהפניה.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/p/גאטו+עוף+3+ק</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>כתובות 404 ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>לא אותר קישור פנימי לכתובת; לאתר את המקור (canonical, hreflang, קובץ סטטי או קישור חיצוני) ולתקן. אין צורך בהפניה.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhaim1.com/p/חטיף+לכלבים+ג'רקי+טיים+רצועות+כבש+80+גרם+-+JERKY+TIME+SOFT+LAMB+FILLET+80G</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>כתובות 404 ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>לא אותר קישור פנימי לכתובת; לאתר את המקור (canonical, hreflang, קובץ סטטי או קישור חיצוני) ולתקן. אין צורך בהפניה.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t>https://www.mhaim1.com/cdn-cgi/l/email-protection</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>404</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
         <v>8868</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>https://www.mhaim1.com/
 https://www.mhaim1.com/page/אודותינו
@@ -69721,45 +70843,45 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>קישור הגנת דוא"ל של Cloudflare (cdn-cgi). גוגל מתעלם מכתובות cdn-cgi; לא נדרש טיפול. ניתן לבטל את Email Address Obfuscation ב-Cloudflare כדי שהסורקים לא ידווחו על כך.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>http://www.mhaim1.com/cdn-cgi/l/email-protection</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B32" s="2" t="n">
         <v>404</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>https://www.mhaim1.com/
 https://www.mhaim1.com/page/אודותינו
@@ -69774,18 +70896,18 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>קישור הגנת דוא"ל של Cloudflare (cdn-cgi). גוגל מתעלם מכתובות cdn-cgi; לא נדרש טיפול. ניתן לבטל את Email Address Obfuscation ב-Cloudflare כדי שהסורקים לא ידווחו על כך.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -69796,7 +70918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -71042,7 +72164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
